--- a/Notes and data for listed articles/(row 4) data for 2023 Wan et al./raw_data/data_for_number_platform_crossed.xlsx
+++ b/Notes and data for listed articles/(row 4) data for 2023 Wan et al./raw_data/data_for_number_platform_crossed.xlsx
@@ -109,7 +109,7 @@
     <xdr:ext cx="2647950" cy="3133725"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image2.png" title="Image"/>
+        <xdr:cNvPr id="0" name="image1.png" title="Image"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -137,7 +137,7 @@
     <xdr:ext cx="4171950" cy="2562225"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image1.png" title="Image"/>
+        <xdr:cNvPr id="0" name="image2.png" title="Image"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>

--- a/Notes and data for listed articles/(row 4) data for 2023 Wan et al./raw_data/data_for_number_platform_crossed.xlsx
+++ b/Notes and data for listed articles/(row 4) data for 2023 Wan et al./raw_data/data_for_number_platform_crossed.xlsx
@@ -109,7 +109,7 @@
     <xdr:ext cx="2647950" cy="3133725"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image1.png" title="Image"/>
+        <xdr:cNvPr id="0" name="image2.png" title="Image"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -137,7 +137,7 @@
     <xdr:ext cx="4171950" cy="2562225"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image2.png" title="Image"/>
+        <xdr:cNvPr id="0" name="image1.png" title="Image"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
